--- a/reports/raw-views/assets/tables/meso_category_counts.xlsx
+++ b/reports/raw-views/assets/tables/meso_category_counts.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Autores</t>
+          <t>Authors</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pares</t>
+          <t>Peers</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Analistas</t>
+          <t>Analysts</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>AI</t>
         </is>
       </c>
     </row>
